--- a/KakeiboAppBackEnd/src/main/resources/textfile/b_詳細設計/画面設計/個別情報画面/インターフェース.xlsx
+++ b/KakeiboAppBackEnd/src/main/resources/textfile/b_詳細設計/画面設計/個別情報画面/インターフェース.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjk037_\Desktop\学習用\家計管理アプリ\b_詳細設計\画面設計\個別情報画面\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C78DE6F-1391-473E-B46D-FB3189C2684F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED8D58F-DE07-441C-B45D-CA6258FCA6D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-180" yWindow="0" windowWidth="12225" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1545" yWindow="90" windowWidth="13860" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="個別収支情報画面" sheetId="6" r:id="rId1"/>
@@ -504,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF988F84-91E3-4D12-B03B-8F9D37C3E9D9}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="15.25" bestFit="1" customWidth="1"/>
@@ -553,7 +553,7 @@
         <v>4700</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:5">
       <c r="B17" t="s">
         <v>4</v>
       </c>
@@ -561,7 +561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
+    <row r="20" spans="2:5">
       <c r="B20" t="s">
         <v>10</v>
       </c>
@@ -569,14 +569,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:5">
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" t="s">
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" t="s">
         <v>11</v>
       </c>
     </row>
